--- a/Test Results/Excel/Vulnerability_Test_Report.xlsx
+++ b/Test Results/Excel/Vulnerability_Test_Report.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Executed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Passed Tests" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Failed Tests" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Execution Metrics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Skipped Tests" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Execution Metrics" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Defect Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 14:11:17 | Total Test Cases: 300</t>
+          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-28 08:48:54 | Total Test Cases: 300</t>
         </is>
       </c>
     </row>
@@ -609,11 +611,11 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -659,7 +661,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -709,11 +711,11 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -759,11 +761,11 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -809,11 +811,11 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -859,11 +861,11 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -909,7 +911,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -959,7 +961,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.64</v>
+        <v>0.13</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1009,7 +1011,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.57</v>
+        <v>0.15</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1059,7 +1061,7 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6</v>
+        <v>0.14</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1109,11 +1111,11 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1159,11 +1161,11 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1209,11 +1211,11 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1259,11 +1261,11 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1311,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.41</v>
+        <v>0.11</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1359,11 +1361,11 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1409,11 +1411,11 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1461,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1509,11 +1511,11 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1559,11 +1561,11 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.64</v>
+        <v>0.28</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1609,11 +1611,11 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1659,11 +1661,11 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1709,11 +1711,11 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1761,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.19</v>
+        <v>0.51</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -1809,7 +1811,7 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.57</v>
+        <v>0.04</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -1859,11 +1861,11 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1911,7 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -1959,7 +1961,7 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -2009,11 +2011,11 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2061,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -2109,11 +2111,11 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2161,7 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0.55</v>
+        <v>0.24</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2209,7 +2211,7 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2259,11 +2261,11 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2309,11 +2311,11 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2361,7 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -2409,11 +2411,11 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2459,11 +2461,11 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2511,7 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -2559,7 +2561,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>0.37</v>
+        <v>0.09</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -2609,7 +2611,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2663,7 +2665,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2711,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -2759,7 +2761,7 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2809,11 +2811,11 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2859,11 +2861,11 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2911,7 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.09</v>
+        <v>0.42</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -2959,11 +2961,11 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3011,7 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.62</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3059,11 +3061,11 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3111,7 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -3159,7 +3161,7 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -3209,11 +3211,11 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3259,11 +3261,11 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3311,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3359,11 +3361,11 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3409,11 +3411,11 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3459,11 +3461,11 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3511,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -3559,11 +3561,11 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3609,11 +3611,11 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3659,11 +3661,11 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3711,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>0.1</v>
+        <v>0.64</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -3759,7 +3761,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -3809,7 +3811,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0.31</v>
+        <v>0.46</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -3859,11 +3861,11 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3911,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
@@ -3959,11 +3961,11 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0.09</v>
+        <v>0.48</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4011,7 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
@@ -4059,11 +4061,11 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4111,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0.41</v>
+        <v>0.59</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
@@ -4159,7 +4161,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0.59</v>
+        <v>0.14</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -4209,7 +4211,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
@@ -4259,7 +4261,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
@@ -4309,7 +4311,7 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>0.53</v>
+        <v>0.08</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -4359,7 +4361,7 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
@@ -4409,11 +4411,11 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4459,11 +4461,11 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4509,11 +4511,11 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4561,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
@@ -4609,11 +4611,11 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>0.27</v>
+        <v>0.61</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4661,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>0.48</v>
+        <v>0.08</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
@@ -4709,7 +4711,7 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
@@ -4759,11 +4761,11 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>0.59</v>
+        <v>0.2</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4809,11 +4811,11 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>0.41</v>
+        <v>0.54</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4859,11 +4861,11 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>0.17</v>
+        <v>0.51</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4909,11 +4911,11 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4961,7 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
@@ -5009,11 +5011,11 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5059,11 +5061,11 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5111,7 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -5159,11 +5161,11 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5209,11 +5211,11 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5259,11 +5261,11 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5309,11 +5311,11 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5359,11 +5361,11 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5411,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
@@ -5459,11 +5461,11 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5511,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>0.42</v>
+        <v>0.05</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
@@ -5559,7 +5561,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
@@ -5609,7 +5611,7 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
@@ -5659,11 +5661,11 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5709,11 +5711,11 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5761,7 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
@@ -5809,11 +5811,11 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5859,11 +5861,11 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>0.52</v>
+        <v>0.19</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5911,7 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
@@ -5959,11 +5961,11 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>0.55</v>
+        <v>0.14</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6009,11 +6011,11 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6061,7 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
@@ -6109,11 +6111,11 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6159,11 +6161,11 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>0.62</v>
+        <v>0.18</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6211,7 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -6259,11 +6261,11 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>0.33</v>
+        <v>0.1</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6309,11 +6311,11 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6359,11 +6361,11 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6409,11 +6411,11 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>0.12</v>
+        <v>0.31</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6461,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
@@ -6509,7 +6511,7 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
@@ -6559,7 +6561,7 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
@@ -6609,11 +6611,11 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6659,11 +6661,11 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>0.51</v>
+        <v>0.14</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6709,11 +6711,11 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6759,11 +6761,11 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>0.09</v>
+        <v>0.39</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6811,7 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>0.58</v>
+        <v>0.35</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
@@ -6859,7 +6861,7 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
@@ -6909,11 +6911,11 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6961,7 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
@@ -7009,11 +7011,11 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>0.55</v>
+        <v>0.11</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7061,7 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
@@ -7109,11 +7111,11 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7161,7 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>0.04</v>
+        <v>0.54</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
@@ -7209,7 +7211,7 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>0.38</v>
+        <v>0.04</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
@@ -7259,7 +7261,7 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -7309,11 +7311,11 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7361,7 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
@@ -7409,7 +7411,7 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>0.24</v>
+        <v>0.42</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
@@ -7459,11 +7461,11 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7509,11 +7511,11 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7561,7 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
@@ -7609,11 +7611,11 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7661,7 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>0.13</v>
+        <v>0.55</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
@@ -7709,11 +7711,11 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>0.22</v>
+        <v>0.55</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7761,7 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
@@ -7809,7 +7811,7 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
@@ -7859,11 +7861,11 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7909,11 +7911,11 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7961,7 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
@@ -8009,7 +8011,7 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
@@ -8059,11 +8061,11 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8111,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>0.09</v>
+        <v>0.43</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -8159,11 +8161,11 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -8209,11 +8211,11 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8261,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
@@ -8309,7 +8311,7 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -8359,11 +8361,11 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>0.28</v>
+        <v>0.65</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8411,7 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>0.26</v>
+        <v>0.55</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
@@ -8459,11 +8461,11 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -8509,11 +8511,11 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -8559,11 +8561,11 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8611,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -8659,7 +8661,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -8709,11 +8711,11 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -8759,11 +8761,11 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>0.19</v>
+        <v>0.59</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8811,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
@@ -8859,7 +8861,7 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
@@ -8909,7 +8911,7 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
@@ -8959,7 +8961,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>0.48</v>
+        <v>0.22</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
@@ -9009,11 +9011,11 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9061,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
@@ -9109,11 +9111,11 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -9159,11 +9161,11 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>0.29</v>
+        <v>0.06</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -9209,11 +9211,11 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -9259,11 +9261,11 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9311,7 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>0.05</v>
+        <v>0.43</v>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
@@ -9359,11 +9361,11 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9411,7 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
@@ -9459,7 +9461,7 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
@@ -9509,7 +9511,7 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
@@ -9559,7 +9561,7 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
@@ -9609,11 +9611,11 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -9659,11 +9661,11 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>0.57</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9711,7 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
@@ -9759,7 +9761,7 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
@@ -9809,7 +9811,7 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>0.58</v>
+        <v>0.13</v>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
@@ -9859,7 +9861,7 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J190" s="4" t="inlineStr">
         <is>
@@ -9909,11 +9911,11 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>0.04</v>
+        <v>0.41</v>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9961,7 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
@@ -10009,11 +10011,11 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -10059,11 +10061,11 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10109,11 +10111,11 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10159,11 +10161,11 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10211,7 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>0.06</v>
+        <v>0.58</v>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
@@ -10259,7 +10261,7 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
@@ -10309,11 +10311,11 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>0.12</v>
+        <v>0.63</v>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10361,7 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>0.19</v>
+        <v>0.57</v>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
@@ -10409,7 +10411,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
@@ -10459,7 +10461,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
@@ -10509,7 +10511,7 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -10559,7 +10561,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>0.35</v>
+        <v>0.04</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -10609,11 +10611,11 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10659,11 +10661,11 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10711,7 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>0.63</v>
+        <v>0.31</v>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
@@ -10759,11 +10761,11 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>0.63</v>
+        <v>0.14</v>
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10811,7 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>0.03</v>
+        <v>0.37</v>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
@@ -10859,11 +10861,11 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10911,7 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>0.49</v>
+        <v>0.17</v>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
@@ -10959,7 +10961,7 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
@@ -11009,11 +11011,11 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11061,7 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
@@ -11109,7 +11111,7 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
@@ -11159,11 +11161,11 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>0.13</v>
+        <v>0.51</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11209,11 +11211,11 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11261,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
@@ -11309,11 +11311,11 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11359,11 +11361,11 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>0.15</v>
+        <v>0.63</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -11409,11 +11411,11 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>0.15</v>
+        <v>0.61</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11461,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
@@ -11509,11 +11511,11 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11559,11 +11561,11 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11611,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
@@ -11659,7 +11661,7 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
@@ -11709,7 +11711,7 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
@@ -11759,7 +11761,7 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
@@ -11809,11 +11811,11 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>0.51</v>
+        <v>0.25</v>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11861,7 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
@@ -11909,7 +11911,7 @@
         </is>
       </c>
       <c r="I231" s="4" t="n">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
@@ -11959,11 +11961,11 @@
         </is>
       </c>
       <c r="I232" s="4" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12011,7 @@
         </is>
       </c>
       <c r="I233" s="4" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
@@ -12059,7 +12061,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
@@ -12109,11 +12111,11 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12161,7 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
@@ -12209,11 +12211,11 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12259,11 +12261,11 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12311,7 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
@@ -12359,11 +12361,11 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>0.08</v>
+        <v>0.6</v>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -12409,7 +12411,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -12459,11 +12461,11 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12511,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>0.62</v>
+        <v>0.06</v>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
@@ -12559,11 +12561,11 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12609,11 +12611,11 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -12659,11 +12661,11 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12709,11 +12711,11 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12761,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>0.46</v>
+        <v>0.14</v>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
@@ -12809,11 +12811,11 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12861,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
@@ -12909,7 +12911,7 @@
         </is>
       </c>
       <c r="I251" s="4" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
@@ -12959,11 +12961,11 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -13009,7 +13011,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>0.26</v>
+        <v>0.55</v>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
@@ -13059,11 +13061,11 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>0.47</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13109,7 +13111,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
@@ -13159,11 +13161,11 @@
         </is>
       </c>
       <c r="I256" s="4" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -13209,11 +13211,11 @@
         </is>
       </c>
       <c r="I257" s="4" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13261,7 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>0.16</v>
+        <v>0.54</v>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
@@ -13309,11 +13311,11 @@
         </is>
       </c>
       <c r="I259" s="4" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13361,7 @@
         </is>
       </c>
       <c r="I260" s="4" t="n">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
@@ -13409,7 +13411,7 @@
         </is>
       </c>
       <c r="I261" s="4" t="n">
-        <v>0.46</v>
+        <v>0.18</v>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
@@ -13459,7 +13461,7 @@
         </is>
       </c>
       <c r="I262" s="4" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
@@ -13509,7 +13511,7 @@
         </is>
       </c>
       <c r="I263" s="4" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
@@ -13559,7 +13561,7 @@
         </is>
       </c>
       <c r="I264" s="4" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
@@ -13609,11 +13611,11 @@
         </is>
       </c>
       <c r="I265" s="4" t="n">
-        <v>0.14</v>
+        <v>0.49</v>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13661,7 @@
         </is>
       </c>
       <c r="I266" s="4" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
@@ -13709,11 +13711,11 @@
         </is>
       </c>
       <c r="I267" s="4" t="n">
-        <v>0.58</v>
+        <v>0.06</v>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -13759,7 +13761,7 @@
         </is>
       </c>
       <c r="I268" s="4" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
@@ -13809,11 +13811,11 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -13859,11 +13861,11 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13911,7 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>0.37</v>
+        <v>0.65</v>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
@@ -13959,11 +13961,11 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="J272" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14011,7 @@
         </is>
       </c>
       <c r="I273" s="4" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="J273" s="4" t="inlineStr">
         <is>
@@ -14059,7 +14061,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>0.17</v>
+        <v>0.53</v>
       </c>
       <c r="J274" s="4" t="inlineStr">
         <is>
@@ -14109,11 +14111,11 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>0.46</v>
+        <v>0.03</v>
       </c>
       <c r="J275" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14161,7 @@
         </is>
       </c>
       <c r="I276" s="4" t="n">
-        <v>0.62</v>
+        <v>0.11</v>
       </c>
       <c r="J276" s="4" t="inlineStr">
         <is>
@@ -14209,7 +14211,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J277" s="4" t="inlineStr">
         <is>
@@ -14259,11 +14261,11 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="J278" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14311,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
@@ -14359,7 +14361,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>0.14</v>
+        <v>0.59</v>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
@@ -14409,11 +14411,11 @@
         </is>
       </c>
       <c r="I281" s="4" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -14459,11 +14461,11 @@
         </is>
       </c>
       <c r="I282" s="4" t="n">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -14509,11 +14511,11 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -14559,11 +14561,11 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>0.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -14609,11 +14611,11 @@
         </is>
       </c>
       <c r="I285" s="4" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14659,11 +14661,11 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>0.19</v>
+        <v>0.51</v>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -14709,11 +14711,11 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14759,11 +14761,11 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>0.63</v>
+        <v>0.23</v>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14811,7 @@
         </is>
       </c>
       <c r="I289" s="4" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
@@ -14859,7 +14861,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
@@ -14909,11 +14911,11 @@
         </is>
       </c>
       <c r="I291" s="4" t="n">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14959,7 +14961,7 @@
         </is>
       </c>
       <c r="I292" s="4" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
@@ -15009,11 +15011,11 @@
         </is>
       </c>
       <c r="I293" s="4" t="n">
-        <v>0.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15059,11 +15061,11 @@
         </is>
       </c>
       <c r="I294" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15109,7 +15111,7 @@
         </is>
       </c>
       <c r="I295" s="4" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
@@ -15159,11 +15161,11 @@
         </is>
       </c>
       <c r="I296" s="4" t="n">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -15209,11 +15211,11 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15259,7 +15261,7 @@
         </is>
       </c>
       <c r="I298" s="4" t="n">
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
@@ -15309,11 +15311,11 @@
         </is>
       </c>
       <c r="I299" s="4" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15361,7 @@
         </is>
       </c>
       <c r="I300" s="4" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
@@ -15409,7 +15411,7 @@
         </is>
       </c>
       <c r="I301" s="4" t="n">
-        <v>0.28</v>
+        <v>0.51</v>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
@@ -15459,7 +15461,7 @@
         </is>
       </c>
       <c r="I302" s="4" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
@@ -15509,7 +15511,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="n">
-        <v>0.62</v>
+        <v>0.29</v>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
@@ -15559,11 +15561,11 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15687,11 +15689,11 @@
         </is>
       </c>
       <c r="I2" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15739,7 @@
         </is>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
@@ -15787,11 +15789,11 @@
         </is>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15837,11 +15839,11 @@
         </is>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15887,11 +15889,11 @@
         </is>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15937,11 +15939,11 @@
         </is>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15987,7 +15989,7 @@
         </is>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
@@ -16037,7 +16039,7 @@
         </is>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.64</v>
+        <v>0.13</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
@@ -16087,7 +16089,7 @@
         </is>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.57</v>
+        <v>0.15</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
@@ -16137,7 +16139,7 @@
         </is>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.6</v>
+        <v>0.14</v>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
@@ -16187,11 +16189,11 @@
         </is>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16237,11 +16239,11 @@
         </is>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16287,11 +16289,11 @@
         </is>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16337,11 +16339,11 @@
         </is>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16387,7 +16389,7 @@
         </is>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.41</v>
+        <v>0.11</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
@@ -16437,11 +16439,11 @@
         </is>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16487,11 +16489,11 @@
         </is>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16537,7 +16539,7 @@
         </is>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
@@ -16587,11 +16589,11 @@
         </is>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16637,11 +16639,11 @@
         </is>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.64</v>
+        <v>0.28</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16687,11 +16689,11 @@
         </is>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16737,11 +16739,11 @@
         </is>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16787,11 +16789,11 @@
         </is>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16839,7 @@
         </is>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.19</v>
+        <v>0.51</v>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
@@ -16887,7 +16889,7 @@
         </is>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.57</v>
+        <v>0.04</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
@@ -16937,11 +16939,11 @@
         </is>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16989,7 @@
         </is>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
@@ -17037,7 +17039,7 @@
         </is>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
@@ -17087,11 +17089,11 @@
         </is>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17137,7 +17139,7 @@
         </is>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
@@ -17187,11 +17189,11 @@
         </is>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17237,7 +17239,7 @@
         </is>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.55</v>
+        <v>0.24</v>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
@@ -17287,7 +17289,7 @@
         </is>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
@@ -17337,11 +17339,11 @@
         </is>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -17387,11 +17389,11 @@
         </is>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -17437,7 +17439,7 @@
         </is>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
@@ -17487,11 +17489,11 @@
         </is>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17537,11 +17539,11 @@
         </is>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.54</v>
+        <v>0.21</v>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17589,7 @@
         </is>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
@@ -17637,7 +17639,7 @@
         </is>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.37</v>
+        <v>0.09</v>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
@@ -17687,7 +17689,7 @@
         </is>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
@@ -17741,7 +17743,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17787,7 +17789,7 @@
         </is>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
@@ -17837,7 +17839,7 @@
         </is>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
@@ -17887,11 +17889,11 @@
         </is>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17937,11 +17939,11 @@
         </is>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -17987,7 +17989,7 @@
         </is>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.09</v>
+        <v>0.42</v>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
@@ -18037,11 +18039,11 @@
         </is>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18087,7 +18089,7 @@
         </is>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.62</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
@@ -18137,11 +18139,11 @@
         </is>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18187,7 +18189,7 @@
         </is>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
@@ -18237,7 +18239,7 @@
         </is>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
@@ -18287,11 +18289,11 @@
         </is>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18337,11 +18339,11 @@
         </is>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18387,7 +18389,7 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
@@ -18437,11 +18439,11 @@
         </is>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18487,11 +18489,11 @@
         </is>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -18537,11 +18539,11 @@
         </is>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -18587,7 +18589,7 @@
         </is>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
@@ -18637,11 +18639,11 @@
         </is>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18687,11 +18689,11 @@
         </is>
       </c>
       <c r="I62" s="8" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18737,11 +18739,11 @@
         </is>
       </c>
       <c r="I63" s="8" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -18787,7 +18789,7 @@
         </is>
       </c>
       <c r="I64" s="8" t="n">
-        <v>0.1</v>
+        <v>0.64</v>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
@@ -18837,7 +18839,7 @@
         </is>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
@@ -18887,7 +18889,7 @@
         </is>
       </c>
       <c r="I66" s="8" t="n">
-        <v>0.31</v>
+        <v>0.46</v>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
@@ -18937,11 +18939,11 @@
         </is>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18987,7 +18989,7 @@
         </is>
       </c>
       <c r="I68" s="8" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
@@ -19037,11 +19039,11 @@
         </is>
       </c>
       <c r="I69" s="8" t="n">
-        <v>0.09</v>
+        <v>0.48</v>
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -19087,7 +19089,7 @@
         </is>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
@@ -19137,11 +19139,11 @@
         </is>
       </c>
       <c r="I71" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19189,7 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>0.41</v>
+        <v>0.59</v>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
@@ -19237,7 +19239,7 @@
         </is>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0.59</v>
+        <v>0.14</v>
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
@@ -19287,7 +19289,7 @@
         </is>
       </c>
       <c r="I74" s="8" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
@@ -19337,7 +19339,7 @@
         </is>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
@@ -19387,7 +19389,7 @@
         </is>
       </c>
       <c r="I76" s="8" t="n">
-        <v>0.53</v>
+        <v>0.08</v>
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
@@ -19437,7 +19439,7 @@
         </is>
       </c>
       <c r="I77" s="8" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
@@ -19487,11 +19489,11 @@
         </is>
       </c>
       <c r="I78" s="8" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -19537,11 +19539,11 @@
         </is>
       </c>
       <c r="I79" s="8" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -19587,11 +19589,11 @@
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -19637,7 +19639,7 @@
         </is>
       </c>
       <c r="I81" s="8" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
@@ -19687,11 +19689,11 @@
         </is>
       </c>
       <c r="I82" s="8" t="n">
-        <v>0.27</v>
+        <v>0.61</v>
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -19737,7 +19739,7 @@
         </is>
       </c>
       <c r="I83" s="8" t="n">
-        <v>0.48</v>
+        <v>0.08</v>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
@@ -19787,7 +19789,7 @@
         </is>
       </c>
       <c r="I84" s="8" t="n">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
@@ -19837,11 +19839,11 @@
         </is>
       </c>
       <c r="I85" s="8" t="n">
-        <v>0.59</v>
+        <v>0.2</v>
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -19887,11 +19889,11 @@
         </is>
       </c>
       <c r="I86" s="8" t="n">
-        <v>0.41</v>
+        <v>0.54</v>
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -19937,11 +19939,11 @@
         </is>
       </c>
       <c r="I87" s="8" t="n">
-        <v>0.17</v>
+        <v>0.51</v>
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -19987,11 +19989,11 @@
         </is>
       </c>
       <c r="I88" s="8" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20037,7 +20039,7 @@
         </is>
       </c>
       <c r="I89" s="8" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
@@ -20087,11 +20089,11 @@
         </is>
       </c>
       <c r="I90" s="8" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20137,11 +20139,11 @@
         </is>
       </c>
       <c r="I91" s="8" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20187,7 +20189,7 @@
         </is>
       </c>
       <c r="I92" s="8" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
@@ -20237,11 +20239,11 @@
         </is>
       </c>
       <c r="I93" s="8" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20287,11 +20289,11 @@
         </is>
       </c>
       <c r="I94" s="8" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20337,11 +20339,11 @@
         </is>
       </c>
       <c r="I95" s="8" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20387,11 +20389,11 @@
         </is>
       </c>
       <c r="I96" s="8" t="n">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20437,11 +20439,11 @@
         </is>
       </c>
       <c r="I97" s="8" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20487,7 +20489,7 @@
         </is>
       </c>
       <c r="I98" s="8" t="n">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
@@ -20537,11 +20539,11 @@
         </is>
       </c>
       <c r="I99" s="8" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20587,7 +20589,7 @@
         </is>
       </c>
       <c r="I100" s="8" t="n">
-        <v>0.42</v>
+        <v>0.05</v>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
@@ -20637,7 +20639,7 @@
         </is>
       </c>
       <c r="I101" s="8" t="n">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
@@ -20687,7 +20689,7 @@
         </is>
       </c>
       <c r="I102" s="8" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
@@ -20737,11 +20739,11 @@
         </is>
       </c>
       <c r="I103" s="8" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20787,11 +20789,11 @@
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20837,7 +20839,7 @@
         </is>
       </c>
       <c r="I105" s="8" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
@@ -20887,11 +20889,11 @@
         </is>
       </c>
       <c r="I106" s="8" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20937,11 +20939,11 @@
         </is>
       </c>
       <c r="I107" s="8" t="n">
-        <v>0.52</v>
+        <v>0.19</v>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20989,7 @@
         </is>
       </c>
       <c r="I108" s="8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
@@ -21037,11 +21039,11 @@
         </is>
       </c>
       <c r="I109" s="8" t="n">
-        <v>0.55</v>
+        <v>0.14</v>
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21087,11 +21089,11 @@
         </is>
       </c>
       <c r="I110" s="8" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21137,7 +21139,7 @@
         </is>
       </c>
       <c r="I111" s="8" t="n">
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
@@ -21187,11 +21189,11 @@
         </is>
       </c>
       <c r="I112" s="8" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21237,11 +21239,11 @@
         </is>
       </c>
       <c r="I113" s="8" t="n">
-        <v>0.62</v>
+        <v>0.18</v>
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21289,7 @@
         </is>
       </c>
       <c r="I114" s="8" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
@@ -21337,11 +21339,11 @@
         </is>
       </c>
       <c r="I115" s="8" t="n">
-        <v>0.33</v>
+        <v>0.1</v>
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -21387,11 +21389,11 @@
         </is>
       </c>
       <c r="I116" s="8" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21437,11 +21439,11 @@
         </is>
       </c>
       <c r="I117" s="8" t="n">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -21487,11 +21489,11 @@
         </is>
       </c>
       <c r="I118" s="8" t="n">
-        <v>0.12</v>
+        <v>0.31</v>
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -21537,7 +21539,7 @@
         </is>
       </c>
       <c r="I119" s="8" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
@@ -21587,7 +21589,7 @@
         </is>
       </c>
       <c r="I120" s="8" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
@@ -21637,7 +21639,7 @@
         </is>
       </c>
       <c r="I121" s="8" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="J121" s="8" t="inlineStr">
         <is>
@@ -21687,11 +21689,11 @@
         </is>
       </c>
       <c r="I122" s="8" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21737,11 +21739,11 @@
         </is>
       </c>
       <c r="I123" s="8" t="n">
-        <v>0.51</v>
+        <v>0.14</v>
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -21787,11 +21789,11 @@
         </is>
       </c>
       <c r="I124" s="8" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -21837,11 +21839,11 @@
         </is>
       </c>
       <c r="I125" s="8" t="n">
-        <v>0.09</v>
+        <v>0.39</v>
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21889,7 @@
         </is>
       </c>
       <c r="I126" s="8" t="n">
-        <v>0.58</v>
+        <v>0.35</v>
       </c>
       <c r="J126" s="8" t="inlineStr">
         <is>
@@ -21937,7 +21939,7 @@
         </is>
       </c>
       <c r="I127" s="8" t="n">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
@@ -21987,11 +21989,11 @@
         </is>
       </c>
       <c r="I128" s="8" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -22037,7 +22039,7 @@
         </is>
       </c>
       <c r="I129" s="8" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
@@ -22087,11 +22089,11 @@
         </is>
       </c>
       <c r="I130" s="8" t="n">
-        <v>0.55</v>
+        <v>0.11</v>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22139,7 @@
         </is>
       </c>
       <c r="I131" s="8" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
@@ -22187,11 +22189,11 @@
         </is>
       </c>
       <c r="I132" s="8" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -22237,7 +22239,7 @@
         </is>
       </c>
       <c r="I133" s="8" t="n">
-        <v>0.04</v>
+        <v>0.54</v>
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
@@ -22287,7 +22289,7 @@
         </is>
       </c>
       <c r="I134" s="8" t="n">
-        <v>0.38</v>
+        <v>0.04</v>
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
@@ -22337,7 +22339,7 @@
         </is>
       </c>
       <c r="I135" s="8" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
@@ -22387,11 +22389,11 @@
         </is>
       </c>
       <c r="I136" s="8" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -22437,7 +22439,7 @@
         </is>
       </c>
       <c r="I137" s="8" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
@@ -22487,7 +22489,7 @@
         </is>
       </c>
       <c r="I138" s="8" t="n">
-        <v>0.24</v>
+        <v>0.42</v>
       </c>
       <c r="J138" s="8" t="inlineStr">
         <is>
@@ -22537,11 +22539,11 @@
         </is>
       </c>
       <c r="I139" s="8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -22587,11 +22589,11 @@
         </is>
       </c>
       <c r="I140" s="8" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -22637,7 +22639,7 @@
         </is>
       </c>
       <c r="I141" s="8" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="J141" s="8" t="inlineStr">
         <is>
@@ -22687,11 +22689,11 @@
         </is>
       </c>
       <c r="I142" s="8" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -22737,7 +22739,7 @@
         </is>
       </c>
       <c r="I143" s="8" t="n">
-        <v>0.13</v>
+        <v>0.55</v>
       </c>
       <c r="J143" s="8" t="inlineStr">
         <is>
@@ -22787,11 +22789,11 @@
         </is>
       </c>
       <c r="I144" s="8" t="n">
-        <v>0.22</v>
+        <v>0.55</v>
       </c>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -22837,7 +22839,7 @@
         </is>
       </c>
       <c r="I145" s="8" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="J145" s="8" t="inlineStr">
         <is>
@@ -22887,7 +22889,7 @@
         </is>
       </c>
       <c r="I146" s="8" t="n">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
@@ -22937,11 +22939,11 @@
         </is>
       </c>
       <c r="I147" s="8" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -22987,11 +22989,11 @@
         </is>
       </c>
       <c r="I148" s="8" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23039,7 @@
         </is>
       </c>
       <c r="I149" s="8" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
@@ -23087,7 +23089,7 @@
         </is>
       </c>
       <c r="I150" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J150" s="8" t="inlineStr">
         <is>
@@ -23137,11 +23139,11 @@
         </is>
       </c>
       <c r="I151" s="8" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -23187,7 +23189,7 @@
         </is>
       </c>
       <c r="I152" s="8" t="n">
-        <v>0.09</v>
+        <v>0.43</v>
       </c>
       <c r="J152" s="8" t="inlineStr">
         <is>
@@ -23237,11 +23239,11 @@
         </is>
       </c>
       <c r="I153" s="8" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -23287,11 +23289,11 @@
         </is>
       </c>
       <c r="I154" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="J154" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -23337,7 +23339,7 @@
         </is>
       </c>
       <c r="I155" s="8" t="n">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="J155" s="8" t="inlineStr">
         <is>
@@ -23387,7 +23389,7 @@
         </is>
       </c>
       <c r="I156" s="8" t="n">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="J156" s="8" t="inlineStr">
         <is>
@@ -23437,11 +23439,11 @@
         </is>
       </c>
       <c r="I157" s="8" t="n">
-        <v>0.28</v>
+        <v>0.65</v>
       </c>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -23487,7 +23489,7 @@
         </is>
       </c>
       <c r="I158" s="8" t="n">
-        <v>0.26</v>
+        <v>0.55</v>
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
@@ -23537,11 +23539,11 @@
         </is>
       </c>
       <c r="I159" s="8" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -23587,11 +23589,11 @@
         </is>
       </c>
       <c r="I160" s="8" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -23637,11 +23639,11 @@
         </is>
       </c>
       <c r="I161" s="8" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -23687,7 +23689,7 @@
         </is>
       </c>
       <c r="I162" s="8" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
@@ -23737,7 +23739,7 @@
         </is>
       </c>
       <c r="I163" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J163" s="8" t="inlineStr">
         <is>
@@ -23787,11 +23789,11 @@
         </is>
       </c>
       <c r="I164" s="8" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -23837,11 +23839,11 @@
         </is>
       </c>
       <c r="I165" s="8" t="n">
-        <v>0.19</v>
+        <v>0.59</v>
       </c>
       <c r="J165" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -23887,7 +23889,7 @@
         </is>
       </c>
       <c r="I166" s="8" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
@@ -23937,7 +23939,7 @@
         </is>
       </c>
       <c r="I167" s="8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="J167" s="8" t="inlineStr">
         <is>
@@ -23987,7 +23989,7 @@
         </is>
       </c>
       <c r="I168" s="8" t="n">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="J168" s="8" t="inlineStr">
         <is>
@@ -24037,7 +24039,7 @@
         </is>
       </c>
       <c r="I169" s="8" t="n">
-        <v>0.48</v>
+        <v>0.22</v>
       </c>
       <c r="J169" s="8" t="inlineStr">
         <is>
@@ -24087,11 +24089,11 @@
         </is>
       </c>
       <c r="I170" s="8" t="n">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c r="J170" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24139,7 @@
         </is>
       </c>
       <c r="I171" s="8" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="J171" s="8" t="inlineStr">
         <is>
@@ -24187,11 +24189,11 @@
         </is>
       </c>
       <c r="I172" s="8" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="J172" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -24237,11 +24239,11 @@
         </is>
       </c>
       <c r="I173" s="8" t="n">
-        <v>0.29</v>
+        <v>0.06</v>
       </c>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24287,11 +24289,11 @@
         </is>
       </c>
       <c r="I174" s="8" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -24337,11 +24339,11 @@
         </is>
       </c>
       <c r="I175" s="8" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24387,7 +24389,7 @@
         </is>
       </c>
       <c r="I176" s="8" t="n">
-        <v>0.05</v>
+        <v>0.43</v>
       </c>
       <c r="J176" s="8" t="inlineStr">
         <is>
@@ -24437,11 +24439,11 @@
         </is>
       </c>
       <c r="I177" s="8" t="n">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24487,7 +24489,7 @@
         </is>
       </c>
       <c r="I178" s="8" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
@@ -24537,7 +24539,7 @@
         </is>
       </c>
       <c r="I179" s="8" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="J179" s="8" t="inlineStr">
         <is>
@@ -24587,7 +24589,7 @@
         </is>
       </c>
       <c r="I180" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="J180" s="8" t="inlineStr">
         <is>
@@ -24637,7 +24639,7 @@
         </is>
       </c>
       <c r="I181" s="8" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="J181" s="8" t="inlineStr">
         <is>
@@ -24687,11 +24689,11 @@
         </is>
       </c>
       <c r="I182" s="8" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -24737,11 +24739,11 @@
         </is>
       </c>
       <c r="I183" s="8" t="n">
-        <v>0.57</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24787,7 +24789,7 @@
         </is>
       </c>
       <c r="I184" s="8" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="J184" s="8" t="inlineStr">
         <is>
@@ -24837,7 +24839,7 @@
         </is>
       </c>
       <c r="I185" s="8" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="J185" s="8" t="inlineStr">
         <is>
@@ -24887,7 +24889,7 @@
         </is>
       </c>
       <c r="I186" s="8" t="n">
-        <v>0.58</v>
+        <v>0.13</v>
       </c>
       <c r="J186" s="8" t="inlineStr">
         <is>
@@ -24937,7 +24939,7 @@
         </is>
       </c>
       <c r="I187" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J187" s="8" t="inlineStr">
         <is>
@@ -24987,11 +24989,11 @@
         </is>
       </c>
       <c r="I188" s="8" t="n">
-        <v>0.04</v>
+        <v>0.41</v>
       </c>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -25037,7 +25039,7 @@
         </is>
       </c>
       <c r="I189" s="8" t="n">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="J189" s="8" t="inlineStr">
         <is>
@@ -25087,11 +25089,11 @@
         </is>
       </c>
       <c r="I190" s="8" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -25137,11 +25139,11 @@
         </is>
       </c>
       <c r="I191" s="8" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J191" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25187,11 +25189,11 @@
         </is>
       </c>
       <c r="I192" s="8" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="J192" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25237,11 +25239,11 @@
         </is>
       </c>
       <c r="I193" s="8" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J193" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -25287,7 +25289,7 @@
         </is>
       </c>
       <c r="I194" s="8" t="n">
-        <v>0.06</v>
+        <v>0.58</v>
       </c>
       <c r="J194" s="8" t="inlineStr">
         <is>
@@ -25337,7 +25339,7 @@
         </is>
       </c>
       <c r="I195" s="8" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="J195" s="8" t="inlineStr">
         <is>
@@ -25387,11 +25389,11 @@
         </is>
       </c>
       <c r="I196" s="8" t="n">
-        <v>0.12</v>
+        <v>0.63</v>
       </c>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25437,7 +25439,7 @@
         </is>
       </c>
       <c r="I197" s="8" t="n">
-        <v>0.19</v>
+        <v>0.57</v>
       </c>
       <c r="J197" s="8" t="inlineStr">
         <is>
@@ -25487,7 +25489,7 @@
         </is>
       </c>
       <c r="I198" s="8" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="J198" s="8" t="inlineStr">
         <is>
@@ -25537,7 +25539,7 @@
         </is>
       </c>
       <c r="I199" s="8" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="J199" s="8" t="inlineStr">
         <is>
@@ -25587,7 +25589,7 @@
         </is>
       </c>
       <c r="I200" s="8" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="J200" s="8" t="inlineStr">
         <is>
@@ -25637,7 +25639,7 @@
         </is>
       </c>
       <c r="I201" s="8" t="n">
-        <v>0.35</v>
+        <v>0.04</v>
       </c>
       <c r="J201" s="8" t="inlineStr">
         <is>
@@ -25687,11 +25689,11 @@
         </is>
       </c>
       <c r="I202" s="8" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="J202" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25737,11 +25739,11 @@
         </is>
       </c>
       <c r="I203" s="8" t="n">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="J203" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25787,7 +25789,7 @@
         </is>
       </c>
       <c r="I204" s="8" t="n">
-        <v>0.63</v>
+        <v>0.31</v>
       </c>
       <c r="J204" s="8" t="inlineStr">
         <is>
@@ -25837,11 +25839,11 @@
         </is>
       </c>
       <c r="I205" s="8" t="n">
-        <v>0.63</v>
+        <v>0.14</v>
       </c>
       <c r="J205" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25887,7 +25889,7 @@
         </is>
       </c>
       <c r="I206" s="8" t="n">
-        <v>0.03</v>
+        <v>0.37</v>
       </c>
       <c r="J206" s="8" t="inlineStr">
         <is>
@@ -25937,11 +25939,11 @@
         </is>
       </c>
       <c r="I207" s="8" t="n">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="J207" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -25987,7 +25989,7 @@
         </is>
       </c>
       <c r="I208" s="8" t="n">
-        <v>0.49</v>
+        <v>0.17</v>
       </c>
       <c r="J208" s="8" t="inlineStr">
         <is>
@@ -26037,7 +26039,7 @@
         </is>
       </c>
       <c r="I209" s="8" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="J209" s="8" t="inlineStr">
         <is>
@@ -26087,11 +26089,11 @@
         </is>
       </c>
       <c r="I210" s="8" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="J210" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -26137,7 +26139,7 @@
         </is>
       </c>
       <c r="I211" s="8" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="J211" s="8" t="inlineStr">
         <is>
@@ -26187,7 +26189,7 @@
         </is>
       </c>
       <c r="I212" s="8" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="J212" s="8" t="inlineStr">
         <is>
@@ -26237,11 +26239,11 @@
         </is>
       </c>
       <c r="I213" s="8" t="n">
-        <v>0.13</v>
+        <v>0.51</v>
       </c>
       <c r="J213" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26287,11 +26289,11 @@
         </is>
       </c>
       <c r="I214" s="8" t="n">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
       <c r="J214" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -26337,7 +26339,7 @@
         </is>
       </c>
       <c r="I215" s="8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J215" s="8" t="inlineStr">
         <is>
@@ -26387,11 +26389,11 @@
         </is>
       </c>
       <c r="I216" s="8" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="J216" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26437,11 +26439,11 @@
         </is>
       </c>
       <c r="I217" s="8" t="n">
-        <v>0.15</v>
+        <v>0.63</v>
       </c>
       <c r="J217" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -26487,11 +26489,11 @@
         </is>
       </c>
       <c r="I218" s="8" t="n">
-        <v>0.15</v>
+        <v>0.61</v>
       </c>
       <c r="J218" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26537,7 +26539,7 @@
         </is>
       </c>
       <c r="I219" s="8" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="J219" s="8" t="inlineStr">
         <is>
@@ -26587,11 +26589,11 @@
         </is>
       </c>
       <c r="I220" s="8" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="J220" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26637,11 +26639,11 @@
         </is>
       </c>
       <c r="I221" s="8" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="J221" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26687,7 +26689,7 @@
         </is>
       </c>
       <c r="I222" s="8" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="J222" s="8" t="inlineStr">
         <is>
@@ -26737,7 +26739,7 @@
         </is>
       </c>
       <c r="I223" s="8" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="J223" s="8" t="inlineStr">
         <is>
@@ -26787,7 +26789,7 @@
         </is>
       </c>
       <c r="I224" s="8" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="J224" s="8" t="inlineStr">
         <is>
@@ -26837,7 +26839,7 @@
         </is>
       </c>
       <c r="I225" s="8" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="J225" s="8" t="inlineStr">
         <is>
@@ -26887,11 +26889,11 @@
         </is>
       </c>
       <c r="I226" s="8" t="n">
-        <v>0.51</v>
+        <v>0.25</v>
       </c>
       <c r="J226" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26937,7 +26939,7 @@
         </is>
       </c>
       <c r="I227" s="8" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="J227" s="8" t="inlineStr">
         <is>
@@ -26987,7 +26989,7 @@
         </is>
       </c>
       <c r="I228" s="8" t="n">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="J228" s="8" t="inlineStr">
         <is>
@@ -27037,11 +27039,11 @@
         </is>
       </c>
       <c r="I229" s="8" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="J229" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -27087,7 +27089,7 @@
         </is>
       </c>
       <c r="I230" s="8" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="J230" s="8" t="inlineStr">
         <is>
@@ -27137,7 +27139,7 @@
         </is>
       </c>
       <c r="I231" s="8" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="J231" s="8" t="inlineStr">
         <is>
@@ -27187,11 +27189,11 @@
         </is>
       </c>
       <c r="I232" s="8" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J232" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27237,7 +27239,7 @@
         </is>
       </c>
       <c r="I233" s="8" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="J233" s="8" t="inlineStr">
         <is>
@@ -27287,11 +27289,11 @@
         </is>
       </c>
       <c r="I234" s="8" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="J234" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -27337,11 +27339,11 @@
         </is>
       </c>
       <c r="I235" s="8" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="J235" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -27387,7 +27389,7 @@
         </is>
       </c>
       <c r="I236" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J236" s="8" t="inlineStr">
         <is>
@@ -27437,11 +27439,11 @@
         </is>
       </c>
       <c r="I237" s="8" t="n">
-        <v>0.08</v>
+        <v>0.6</v>
       </c>
       <c r="J237" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27487,7 +27489,7 @@
         </is>
       </c>
       <c r="I238" s="8" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="J238" s="8" t="inlineStr">
         <is>
@@ -27537,11 +27539,11 @@
         </is>
       </c>
       <c r="I239" s="8" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="J239" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27589,7 @@
         </is>
       </c>
       <c r="I240" s="8" t="n">
-        <v>0.62</v>
+        <v>0.06</v>
       </c>
       <c r="J240" s="8" t="inlineStr">
         <is>
@@ -27637,11 +27639,11 @@
         </is>
       </c>
       <c r="I241" s="8" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="J241" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -27687,11 +27689,11 @@
         </is>
       </c>
       <c r="I242" s="8" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="J242" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27737,11 +27739,11 @@
         </is>
       </c>
       <c r="I243" s="8" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J243" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -27787,11 +27789,11 @@
         </is>
       </c>
       <c r="I244" s="8" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="J244" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27837,7 +27839,7 @@
         </is>
       </c>
       <c r="I245" s="8" t="n">
-        <v>0.46</v>
+        <v>0.14</v>
       </c>
       <c r="J245" s="8" t="inlineStr">
         <is>
@@ -27887,11 +27889,11 @@
         </is>
       </c>
       <c r="I246" s="8" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="J246" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27939,7 @@
         </is>
       </c>
       <c r="I247" s="8" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="J247" s="8" t="inlineStr">
         <is>
@@ -27987,7 +27989,7 @@
         </is>
       </c>
       <c r="I248" s="8" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="J248" s="8" t="inlineStr">
         <is>
@@ -28037,11 +28039,11 @@
         </is>
       </c>
       <c r="I249" s="8" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="J249" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -28087,7 +28089,7 @@
         </is>
       </c>
       <c r="I250" s="8" t="n">
-        <v>0.26</v>
+        <v>0.55</v>
       </c>
       <c r="J250" s="8" t="inlineStr">
         <is>
@@ -28137,11 +28139,11 @@
         </is>
       </c>
       <c r="I251" s="8" t="n">
-        <v>0.47</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J251" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -28187,7 +28189,7 @@
         </is>
       </c>
       <c r="I252" s="8" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="J252" s="8" t="inlineStr">
         <is>
@@ -28237,11 +28239,11 @@
         </is>
       </c>
       <c r="I253" s="8" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="J253" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -28287,11 +28289,11 @@
         </is>
       </c>
       <c r="I254" s="8" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="J254" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -28337,7 +28339,7 @@
         </is>
       </c>
       <c r="I255" s="8" t="n">
-        <v>0.16</v>
+        <v>0.54</v>
       </c>
       <c r="J255" s="8" t="inlineStr">
         <is>
@@ -28387,11 +28389,11 @@
         </is>
       </c>
       <c r="I256" s="8" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="J256" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -28437,7 +28439,7 @@
         </is>
       </c>
       <c r="I257" s="8" t="n">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
       <c r="J257" s="8" t="inlineStr">
         <is>
@@ -28487,7 +28489,7 @@
         </is>
       </c>
       <c r="I258" s="8" t="n">
-        <v>0.46</v>
+        <v>0.18</v>
       </c>
       <c r="J258" s="8" t="inlineStr">
         <is>
@@ -28537,7 +28539,7 @@
         </is>
       </c>
       <c r="I259" s="8" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="J259" s="8" t="inlineStr">
         <is>
@@ -28587,7 +28589,7 @@
         </is>
       </c>
       <c r="I260" s="8" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="J260" s="8" t="inlineStr">
         <is>
@@ -28637,7 +28639,7 @@
         </is>
       </c>
       <c r="I261" s="8" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="J261" s="8" t="inlineStr">
         <is>
@@ -28687,11 +28689,11 @@
         </is>
       </c>
       <c r="I262" s="8" t="n">
-        <v>0.14</v>
+        <v>0.49</v>
       </c>
       <c r="J262" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -28737,7 +28739,7 @@
         </is>
       </c>
       <c r="I263" s="8" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="J263" s="8" t="inlineStr">
         <is>
@@ -28787,11 +28789,11 @@
         </is>
       </c>
       <c r="I264" s="8" t="n">
-        <v>0.58</v>
+        <v>0.06</v>
       </c>
       <c r="J264" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -28837,7 +28839,7 @@
         </is>
       </c>
       <c r="I265" s="8" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="J265" s="8" t="inlineStr">
         <is>
@@ -28887,11 +28889,11 @@
         </is>
       </c>
       <c r="I266" s="8" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="J266" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -28937,11 +28939,11 @@
         </is>
       </c>
       <c r="I267" s="8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="J267" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -28987,7 +28989,7 @@
         </is>
       </c>
       <c r="I268" s="8" t="n">
-        <v>0.37</v>
+        <v>0.65</v>
       </c>
       <c r="J268" s="8" t="inlineStr">
         <is>
@@ -29037,11 +29039,11 @@
         </is>
       </c>
       <c r="I269" s="8" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="J269" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29087,7 +29089,7 @@
         </is>
       </c>
       <c r="I270" s="8" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="J270" s="8" t="inlineStr">
         <is>
@@ -29137,7 +29139,7 @@
         </is>
       </c>
       <c r="I271" s="8" t="n">
-        <v>0.17</v>
+        <v>0.53</v>
       </c>
       <c r="J271" s="8" t="inlineStr">
         <is>
@@ -29187,11 +29189,11 @@
         </is>
       </c>
       <c r="I272" s="8" t="n">
-        <v>0.46</v>
+        <v>0.03</v>
       </c>
       <c r="J272" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -29237,7 +29239,7 @@
         </is>
       </c>
       <c r="I273" s="8" t="n">
-        <v>0.62</v>
+        <v>0.11</v>
       </c>
       <c r="J273" s="8" t="inlineStr">
         <is>
@@ -29287,7 +29289,7 @@
         </is>
       </c>
       <c r="I274" s="8" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J274" s="8" t="inlineStr">
         <is>
@@ -29337,11 +29339,11 @@
         </is>
       </c>
       <c r="I275" s="8" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="J275" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29387,7 +29389,7 @@
         </is>
       </c>
       <c r="I276" s="8" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="J276" s="8" t="inlineStr">
         <is>
@@ -29437,7 +29439,7 @@
         </is>
       </c>
       <c r="I277" s="8" t="n">
-        <v>0.14</v>
+        <v>0.59</v>
       </c>
       <c r="J277" s="8" t="inlineStr">
         <is>
@@ -29487,11 +29489,11 @@
         </is>
       </c>
       <c r="I278" s="8" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="J278" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29537,11 +29539,11 @@
         </is>
       </c>
       <c r="I279" s="8" t="n">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
       <c r="J279" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29587,11 +29589,11 @@
         </is>
       </c>
       <c r="I280" s="8" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="J280" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29637,11 +29639,11 @@
         </is>
       </c>
       <c r="I281" s="8" t="n">
-        <v>0.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J281" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29687,11 +29689,11 @@
         </is>
       </c>
       <c r="I282" s="8" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J282" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -29737,11 +29739,11 @@
         </is>
       </c>
       <c r="I283" s="8" t="n">
-        <v>0.19</v>
+        <v>0.51</v>
       </c>
       <c r="J283" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29787,11 +29789,11 @@
         </is>
       </c>
       <c r="I284" s="8" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="J284" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -29837,11 +29839,11 @@
         </is>
       </c>
       <c r="I285" s="8" t="n">
-        <v>0.63</v>
+        <v>0.23</v>
       </c>
       <c r="J285" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -29887,7 +29889,7 @@
         </is>
       </c>
       <c r="I286" s="8" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="J286" s="8" t="inlineStr">
         <is>
@@ -29937,7 +29939,7 @@
         </is>
       </c>
       <c r="I287" s="8" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="J287" s="8" t="inlineStr">
         <is>
@@ -29987,11 +29989,11 @@
         </is>
       </c>
       <c r="I288" s="8" t="n">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="J288" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -30037,7 +30039,7 @@
         </is>
       </c>
       <c r="I289" s="8" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="J289" s="8" t="inlineStr">
         <is>
@@ -30087,11 +30089,11 @@
         </is>
       </c>
       <c r="I290" s="8" t="n">
-        <v>0.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J290" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -30137,11 +30139,11 @@
         </is>
       </c>
       <c r="I291" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J291" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -30187,7 +30189,7 @@
         </is>
       </c>
       <c r="I292" s="8" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="J292" s="8" t="inlineStr">
         <is>
@@ -30237,11 +30239,11 @@
         </is>
       </c>
       <c r="I293" s="8" t="n">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="J293" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -30287,11 +30289,11 @@
         </is>
       </c>
       <c r="I294" s="8" t="n">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
       <c r="J294" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -30337,7 +30339,7 @@
         </is>
       </c>
       <c r="I295" s="8" t="n">
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="J295" s="8" t="inlineStr">
         <is>
@@ -30387,11 +30389,11 @@
         </is>
       </c>
       <c r="I296" s="8" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J296" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -30437,7 +30439,7 @@
         </is>
       </c>
       <c r="I297" s="8" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="J297" s="8" t="inlineStr">
         <is>
@@ -30487,7 +30489,7 @@
         </is>
       </c>
       <c r="I298" s="8" t="n">
-        <v>0.28</v>
+        <v>0.51</v>
       </c>
       <c r="J298" s="8" t="inlineStr">
         <is>
@@ -30537,7 +30539,7 @@
         </is>
       </c>
       <c r="I299" s="8" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="J299" s="8" t="inlineStr">
         <is>
@@ -30587,7 +30589,7 @@
         </is>
       </c>
       <c r="I300" s="8" t="n">
-        <v>0.62</v>
+        <v>0.29</v>
       </c>
       <c r="J300" s="8" t="inlineStr">
         <is>
@@ -30637,11 +30639,11 @@
         </is>
       </c>
       <c r="I301" s="8" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="J301" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -30734,6 +30736,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Test Name</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Latency / Exec Time (s)</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -30821,7 +30901,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>102.35 seconds</t>
+          <t>102.10 seconds</t>
         </is>
       </c>
     </row>
@@ -30857,7 +30937,49 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27 14:11:17</t>
+          <t>2026-07-28 08:48:54</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Defect ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
